--- a/tests/fixtures/northern_peak_sample.xlsx
+++ b/tests/fixtures/northern_peak_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/tests/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_CE685CBB96285ABD108E2FDED034EC30A0E70B29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7B656DA-048F-4B66-AAC9-D379948FB149}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_CE685CBB96285ABD108E2FDED034EC30A0E70B29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7167C6C0-5466-4349-B8A4-3E5FE94BB828}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="542">
   <si>
     <t>CCPC Corporate Tax Planning &amp; Compliance Intake Workbook</t>
   </si>
@@ -1669,6 +1669,12 @@
   </si>
   <si>
     <t>Connected (sister corp under common control, s.186(4)): deductible under s.112, NOT active business income. Part IV = this corp's share of the payer's dividend refund - enter it in the holdco section below.</t>
+  </si>
+  <si>
+    <t>Refundable Portion of SR&amp;ED ITC ($)</t>
+  </si>
+  <si>
+    <t>Cash-refundable part of the ITC (s.127.1). Defaults to the full ITC when the enhanced 35% rate applies (current expenditures of a CCPC under the expenditure limit). Overwrite with the actual refundable amount if part is non-refundable.</t>
   </si>
 </sst>
 </file>
@@ -4228,9 +4234,17 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="16" t="s">
+        <v>540</v>
+      </c>
       <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="C10" s="15">
+        <f>IF(C8="Yes",C9,0)</f>
+        <v>22750</v>
+      </c>
+      <c r="D10" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="62" t="s">
@@ -6027,6 +6041,8 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A5:B5"/>
@@ -6034,8 +6050,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A6:B6"/>

--- a/tests/fixtures/northern_peak_sample.xlsx
+++ b/tests/fixtures/northern_peak_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/tests/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_CE685CBB96285ABD108E2FDED034EC30A0E70B29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7167C6C0-5466-4349-B8A4-3E5FE94BB828}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_CE685CBB96285ABD108E2FDED034EC30A0E70B29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9830F2-AFA5-438F-A521-B08D195DA3A9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="544">
   <si>
     <t>CCPC Corporate Tax Planning &amp; Compliance Intake Workbook</t>
   </si>
@@ -1675,6 +1675,12 @@
   </si>
   <si>
     <t>Cash-refundable part of the ITC (s.127.1). Defaults to the full ITC when the enhanced 35% rate applies (current expenditures of a CCPC under the expenditure limit). Overwrite with the actual refundable amount if part is non-refundable.</t>
+  </si>
+  <si>
+    <t>Refundable Portion of Provincial Credit ($)</t>
+  </si>
+  <si>
+    <t>Part of the provincial credit paid in cash even with no tax owing (e.g., Alberta Innovation Employment Grant). Leave blank if non-refundable - unused amounts then carry forward.</t>
   </si>
 </sst>
 </file>
@@ -2045,15 +2051,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2163,10 +2169,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2680,6 +2682,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="B24:D24"/>
@@ -2696,11 +2703,6 @@
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3656,7 +3658,7 @@
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="63" t="s">
         <v>392</v>
       </c>
       <c r="B9" s="61"/>
@@ -3696,7 +3698,7 @@
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="63" t="s">
         <v>397</v>
       </c>
       <c r="B14" s="61"/>
@@ -3728,7 +3730,7 @@
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="63" t="s">
         <v>400</v>
       </c>
       <c r="B18" s="61"/>
@@ -3795,7 +3797,7 @@
       <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="63" t="s">
         <v>408</v>
       </c>
       <c r="B27" s="61"/>
@@ -3824,6 +3826,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:D3"/>
@@ -3833,12 +3841,6 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3899,7 +3901,7 @@
       <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="60" t="s">
         <v>413</v>
       </c>
       <c r="B4" s="61"/>
@@ -3963,7 +3965,7 @@
       <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="63" t="s">
         <v>419</v>
       </c>
       <c r="B12" s="61"/>
@@ -4058,7 +4060,7 @@
       <c r="C21" s="10"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="63" t="s">
         <v>427</v>
       </c>
       <c r="B22" s="61"/>
@@ -4247,7 +4249,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="63" t="s">
         <v>442</v>
       </c>
       <c r="B11" s="61"/>
@@ -4255,7 +4257,7 @@
       <c r="D11" s="61"/>
     </row>
     <row r="12" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="60" t="s">
         <v>443</v>
       </c>
       <c r="B12" s="61"/>
@@ -4281,12 +4283,19 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="A15" s="67" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="66"/>
+      <c r="C15" s="27">
+        <v>9750</v>
+      </c>
+      <c r="D15" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="63" t="s">
         <v>447</v>
       </c>
       <c r="B16" s="61"/>
@@ -4331,18 +4340,19 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A8:B8"/>
+  <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5296,7 +5306,7 @@
       <c r="D2" s="54"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="63" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="61"/>
@@ -5344,7 +5354,7 @@
       <c r="B9" s="10"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="63" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="61"/>
@@ -5386,7 +5396,7 @@
       <c r="B14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="63" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="61"/>
@@ -5491,7 +5501,7 @@
       <c r="B26" s="10"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="63" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="61"/>
@@ -5568,7 +5578,7 @@
       <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="63" t="s">
         <v>76</v>
       </c>
       <c r="B36" s="61"/>
@@ -5661,7 +5671,7 @@
       <c r="B46" s="10"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="62" t="s">
+      <c r="A47" s="63" t="s">
         <v>86</v>
       </c>
       <c r="B47" s="61"/>
@@ -5727,7 +5737,7 @@
       <c r="B54" s="10"/>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="62" t="s">
+      <c r="A55" s="63" t="s">
         <v>93</v>
       </c>
       <c r="B55" s="61"/>
@@ -5735,7 +5745,7 @@
       <c r="D55" s="61"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="60" t="str">
+      <c r="A56" s="62" t="str">
         <f>IF(B18&gt;0,"• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.","")</f>
         <v>• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.</v>
       </c>
@@ -5744,7 +5754,7 @@
       <c r="D56" s="61"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="60" t="str">
+      <c r="A57" s="62" t="str">
         <f>IF(COUNTIF('8. Shareholders &amp; TOSI'!I5:I20,"Not Excluded - TOSI Risk")&gt;0,"• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.","")</f>
         <v>• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.</v>
       </c>
@@ -5753,7 +5763,7 @@
       <c r="D57" s="61"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="60" t="str">
+      <c r="A58" s="62" t="str">
         <f>IF(B44&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
         <v>• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.</v>
       </c>
@@ -5762,7 +5772,7 @@
       <c r="D58" s="61"/>
     </row>
     <row r="59" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="63" t="s">
+      <c r="A59" s="60" t="s">
         <v>94</v>
       </c>
       <c r="B59" s="61"/>
@@ -5771,12 +5781,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
@@ -5784,6 +5788,12 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6031,6 +6041,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A19:B19"/>
@@ -6043,18 +6065,6 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6428,7 +6438,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="63" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="61"/>
@@ -6473,7 +6483,7 @@
       <c r="B10" s="10"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="63" t="s">
         <v>158</v>
       </c>
       <c r="B11" s="61"/>
@@ -6515,7 +6525,7 @@
       <c r="B16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="63" t="s">
         <v>162</v>
       </c>
       <c r="B17" s="61"/>
@@ -6647,7 +6657,7 @@
       <c r="B33" s="10"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="62" t="s">
+      <c r="A34" s="63" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="61"/>
@@ -6767,7 +6777,7 @@
       <c r="B45" s="10"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="62" t="s">
+      <c r="A46" s="63" t="s">
         <v>193</v>
       </c>
       <c r="B46" s="61"/>
@@ -7001,7 +7011,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="63" t="s">
         <v>224</v>
       </c>
       <c r="B4" s="61"/>
@@ -7106,7 +7116,7 @@
       <c r="B16" s="31"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="63" t="s">
         <v>238</v>
       </c>
       <c r="B17" s="61"/>
@@ -7197,7 +7207,7 @@
       <c r="B28" s="31"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="63" t="s">
         <v>249</v>
       </c>
       <c r="B29" s="61"/>
@@ -7273,7 +7283,7 @@
       <c r="B38" s="31"/>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="62" t="s">
+      <c r="A39" s="63" t="s">
         <v>257</v>
       </c>
       <c r="B39" s="61"/>
@@ -7345,7 +7355,7 @@
       <c r="D2" s="54"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="63" t="s">
         <v>264</v>
       </c>
       <c r="B4" s="61"/>
@@ -7382,7 +7392,7 @@
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="63" t="s">
         <v>268</v>
       </c>
       <c r="B8" s="61"/>
@@ -7407,7 +7417,7 @@
       <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="63" t="s">
         <v>271</v>
       </c>
       <c r="B11" s="61"/>
@@ -7432,7 +7442,7 @@
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="63" t="s">
         <v>274</v>
       </c>
       <c r="B14" s="61"/>
@@ -7499,7 +7509,7 @@
       <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="63" t="s">
         <v>277</v>
       </c>
       <c r="B21" s="61"/>
@@ -7538,7 +7548,7 @@
       <c r="C25" s="10"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="63" t="s">
         <v>278</v>
       </c>
       <c r="B26" s="61"/>
@@ -7577,6 +7587,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
@@ -7585,12 +7601,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/tests/fixtures/northern_peak_sample.xlsx
+++ b/tests/fixtures/northern_peak_sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/207c16c34f2daf9f/Google Drive Docs/Biz Infograph/Claude/tax-planning-agent_rate_llm/tests/fixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhd_s\AppData\Local\Temp\claude\C--Users-mhd-s-OneDrive-Google-Drive-Docs-Biz-Infograph-Claude-tax-planning-agent-rate-llm\e972fdae-35b9-403a-9197-7df442a6acba\scratchpad\dash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_CE685CBB96285ABD108E2FDED034EC30A0E70B29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9830F2-AFA5-438F-A521-B08D195DA3A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E1F1A9-DBE5-47F7-B3B5-6C69EB8D10E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="585">
   <si>
     <t>CCPC Corporate Tax Planning &amp; Compliance Intake Workbook</t>
   </si>
@@ -225,12 +225,6 @@
     <t>Net Active Business Income (this entity)</t>
   </si>
   <si>
-    <t>Aggregate Investment Income (this entity, current year — used as proxy for prior-year AAII test)</t>
-  </si>
-  <si>
-    <t>Passive-Income Grind (reduction to $500K limit: 5 × (AAII − $50,000), capped)</t>
-  </si>
-  <si>
     <t>Group Taxable Capital Employed in Canada (from Associated Corporations tab)</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>This Entity's SBD Limit (lesser of grind-adjusted limit and Schedule 23 allocation)</t>
   </si>
   <si>
-    <t>If associated, pulls this entity's row from the Schedule 23 allocation table by name; if not associated, defaults to the full $500K (post-grind).</t>
-  </si>
-  <si>
     <t>Active Business Income Taxed at SBD Rate</t>
   </si>
   <si>
@@ -255,21 +246,12 @@
     <t>⚠ Passive-Income Grind Flag</t>
   </si>
   <si>
-    <t>2. CURRENT-YEAR CORPORATE TAX ESTIMATE (federal + provincial)</t>
-  </si>
-  <si>
     <t>Tax on SBD-Rate Income</t>
   </si>
   <si>
     <t>Tax on General-Rate Active Business Income</t>
   </si>
   <si>
-    <t>Tax on Aggregate Investment Income</t>
-  </si>
-  <si>
-    <t>ESTIMATED TOTAL CORPORATE TAX PAYABLE</t>
-  </si>
-  <si>
     <t>Less: Instalments Already Paid</t>
   </si>
   <si>
@@ -279,39 +261,18 @@
     <t>Instalments Likely Required Next Year?</t>
   </si>
   <si>
-    <t>3. RDTOH / GRIP / CDA — RECOVERABLE TAX POOLS</t>
-  </si>
-  <si>
-    <t>Non-Eligible RDTOH Addition This Year (≈30⅔% of Aggregate Investment Income)</t>
-  </si>
-  <si>
     <t>Non-Eligible RDTOH — Opening Balance</t>
   </si>
   <si>
-    <t>Non-Eligible RDTOH — Closing Balance (Opening + Addition)</t>
-  </si>
-  <si>
-    <t>Eligible RDTOH — Opening/Closing Balance (carried forward)</t>
-  </si>
-  <si>
     <t>Non-Eligible Dividend Needed to Fully Recover Non-Eligible RDTOH (÷38⅓%)</t>
   </si>
   <si>
     <t>Eligible Dividend Needed to Fully Recover Eligible RDTOH (÷38⅓%)</t>
   </si>
   <si>
-    <t>GRIP Balance Available (for lower-taxed ELIGIBLE dividends)</t>
-  </si>
-  <si>
-    <t>CDA Balance Available (paid 100% TAX-FREE by election — T2054)</t>
-  </si>
-  <si>
     <t>⚠ Action Flag</t>
   </si>
   <si>
-    <t>4. PAYROLL, GST/HST &amp; COMPLIANCE SUMMARY</t>
-  </si>
-  <si>
     <t>Total Salaries &amp; Wages Paid</t>
   </si>
   <si>
@@ -324,15 +285,9 @@
     <t>CCA Claimed This Year (reduces taxable income above — apply manually if not yet reflected)</t>
   </si>
   <si>
-    <t>SR&amp;ED Investment Tax Credit Estimate</t>
-  </si>
-  <si>
     <t>Provincial Credit Estimate</t>
   </si>
   <si>
-    <t>5. PLANNING FLAGS TO DISCUSS WITH YOUR ACCOUNTANT</t>
-  </si>
-  <si>
     <t>• Salary vs. dividend mix for each owner-manager should be modelled against personal marginal rates (see the separate Personal Tax module) — corporate tax alone does not determine the optimal mix.</t>
   </si>
   <si>
@@ -1681,6 +1636,174 @@
   </si>
   <si>
     <t>Part of the provincial credit paid in cash even with no tax owing (e.g., Alberta Innovation Employment Grant). Leave blank if non-refundable - unused amounts then carry forward.</t>
+  </si>
+  <si>
+    <t>Adjusted Aggregate Investment Income (current year — Part I investment income + portfolio dividends)</t>
+  </si>
+  <si>
+    <t>Connected-corporation dividends are excluded. The grind below uses the PRIOR-year figure from '5. Prior-Year Tax Attributes' when entered.</t>
+  </si>
+  <si>
+    <t>Passive-Income Grind (5 × (prior-year adjusted AAII − $50,000), capped; current year used as proxy if prior year blank)</t>
+  </si>
+  <si>
+    <t>If associated, pulls this entity's Schedule 23 allocation by matching its legal name (from Entity Setup) on the Associated Corporations tab; if not found or not associated, defaults to the full $500K (post-grind).</t>
+  </si>
+  <si>
+    <t>2. INVESTMENT INCOME &amp; PART IV TAX</t>
+  </si>
+  <si>
+    <t>Investment-Income Detail Supplied? (holdco section, '3. Income Statement')</t>
+  </si>
+  <si>
+    <t>If No, the single Aggregate Investment Income figure is used for everything below.</t>
+  </si>
+  <si>
+    <t>Part I Investment Income (interest, rents, taxable capital gains)</t>
+  </si>
+  <si>
+    <t>Dividends received are deductible (s.112) and excluded here.</t>
+  </si>
+  <si>
+    <t>Portfolio Dividends Received (non-connected)</t>
+  </si>
+  <si>
+    <t>Connected-Corporation Dividends Received</t>
+  </si>
+  <si>
+    <t>Part IV Tax on Portfolio Dividends (38⅓%)</t>
+  </si>
+  <si>
+    <t>Part IV Tax on Connected Dividends (share of payer's refund)</t>
+  </si>
+  <si>
+    <t>TOTAL PART IV TAX (refundable — added to RDTOH)</t>
+  </si>
+  <si>
+    <t>Non-Taxable Capital Gains (credits the CDA)</t>
+  </si>
+  <si>
+    <t>Equals the taxable portion at a 1/2 inclusion rate.</t>
+  </si>
+  <si>
+    <t>3. CURRENT-YEAR CORPORATE TAX ESTIMATE (federal + provincial)</t>
+  </si>
+  <si>
+    <t>Tax on Part I Investment Income</t>
+  </si>
+  <si>
+    <t>PART I TAX (before credits)</t>
+  </si>
+  <si>
+    <t>Part IV Tax</t>
+  </si>
+  <si>
+    <t>Part III.1 Tax — excessive eligible dividend (20%, if no election)</t>
+  </si>
+  <si>
+    <t>Avoidable by the s.185.1(2) election to treat the excess as non-eligible.</t>
+  </si>
+  <si>
+    <t>Part III Tax — excessive capital dividend (60%, if no election)</t>
+  </si>
+  <si>
+    <t>Avoidable by the s.184(3) election to treat the excess as a taxable dividend.</t>
+  </si>
+  <si>
+    <t>TOTAL TAX PAYABLE BEFORE DIVIDEND REFUND</t>
+  </si>
+  <si>
+    <t>Less: Dividend Refund</t>
+  </si>
+  <si>
+    <t>Less: Credits Applied Against Part I Tax (never below zero)</t>
+  </si>
+  <si>
+    <t>SR&amp;ED ITC + provincial credit reduce Part I tax only — not Part IV, III.1 or III.</t>
+  </si>
+  <si>
+    <t>Less: Refundable Credits Paid in Cash (excess over Part I tax)</t>
+  </si>
+  <si>
+    <t>Paid only once the SR&amp;ED / provincial claim is accepted.</t>
+  </si>
+  <si>
+    <t>NET CORPORATE TAX AFTER CREDITS</t>
+  </si>
+  <si>
+    <t>Unused Non-Refundable Credits (carry forward — NOT in the balance above)</t>
+  </si>
+  <si>
+    <t>4. RDTOH / GRIP / CDA — RECOVERABLE TAX POOLS</t>
+  </si>
+  <si>
+    <t>Non-Eligible RDTOH Addition (30⅔% of Part I investment income + non-eligible Part IV)</t>
+  </si>
+  <si>
+    <t>Non-Eligible RDTOH — Year-End, Before Dividends</t>
+  </si>
+  <si>
+    <t>Eligible RDTOH Addition (eligible portfolio Part IV + connected Part IV from payer's eligible RDTOH)</t>
+  </si>
+  <si>
+    <t>Eligible RDTOH — Year-End, Before Dividends</t>
+  </si>
+  <si>
+    <t>GRIP Addition (0.72 × general-rate ABI + eligible dividends received)</t>
+  </si>
+  <si>
+    <t>GRIP Available at Year-End</t>
+  </si>
+  <si>
+    <t>CDA Addition (non-taxable capital gains + life insurance over ACB)</t>
+  </si>
+  <si>
+    <t>CDA Available at Year-End</t>
+  </si>
+  <si>
+    <t>5. DIVIDENDS PAID THIS YEAR — REFUND &amp; DESIGNATION TESTS</t>
+  </si>
+  <si>
+    <t>Capital Dividends Paid</t>
+  </si>
+  <si>
+    <t>Refund from Non-Eligible RDTOH (non-eligible dividends × 38⅓%)</t>
+  </si>
+  <si>
+    <t>Refund from Eligible RDTOH (eligible dividends, then non-eligible overflow)</t>
+  </si>
+  <si>
+    <t>Eligible dividends recover eligible RDTOH only; non-eligible dividends use non-eligible RDTOH first.</t>
+  </si>
+  <si>
+    <t>TOTAL DIVIDEND REFUND</t>
+  </si>
+  <si>
+    <t>Non-Eligible RDTOH Carried Forward</t>
+  </si>
+  <si>
+    <t>Eligible RDTOH Carried Forward</t>
+  </si>
+  <si>
+    <t>Excessive Eligible Dividend Designation (eligible paid over GRIP)</t>
+  </si>
+  <si>
+    <t>GRIP Carried Forward</t>
+  </si>
+  <si>
+    <t>Excessive Capital Dividend (capital paid over CDA)</t>
+  </si>
+  <si>
+    <t>CDA Carried Forward</t>
+  </si>
+  <si>
+    <t>6. PAYROLL, GST/HST &amp; COMPLIANCE SUMMARY</t>
+  </si>
+  <si>
+    <t>SR&amp;ED Investment Tax Credit Estimate (of which refundable: see Credits tab)</t>
+  </si>
+  <si>
+    <t>7. PLANNING FLAGS TO DISCUSS WITH YOUR ACCOUNTANT</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1818,7 @@
     <numFmt numFmtId="168" formatCode="[$$-409]#,##0.00;[Red]\-[$$-409]#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1761,6 +1884,13 @@
       <sz val="11"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1958,7 +2088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1989,7 +2119,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2051,15 +2180,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2086,6 +2215,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2362,142 +2503,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -2513,69 +2654,69 @@
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -2653,40 +2794,35 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="53" t="s">
+      <c r="A48" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="56" t="s">
+      <c r="A49" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="54"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="54"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="B24:D24"/>
@@ -2703,6 +2839,11 @@
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2730,221 +2871,221 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>320</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="D4" s="34">
+        <v>0.6</v>
+      </c>
+      <c r="E4" s="34">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="27">
+        <v>44</v>
+      </c>
+      <c r="G4" s="27">
+        <v>45</v>
+      </c>
+      <c r="H4" s="27">
+        <v>8</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" s="24">
+        <v>0</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C5" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D5" s="34">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="34">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="27">
+        <v>42</v>
+      </c>
+      <c r="G5" s="27">
+        <v>5</v>
+      </c>
+      <c r="H5" s="27">
+        <v>3</v>
+      </c>
+      <c r="I5" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="J5" s="24">
+        <v>95000</v>
+      </c>
+      <c r="K5" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B6" s="27" t="s">
         <v>326</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="C6" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="D6" s="34">
+        <v>0</v>
+      </c>
+      <c r="E6" s="34">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27">
+        <v>0</v>
+      </c>
+      <c r="H6" s="27">
+        <v>0</v>
+      </c>
+      <c r="I6" s="27" t="s">
         <v>328</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J6" s="24">
+        <v>0</v>
+      </c>
+      <c r="K6" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="D4" s="35">
-        <v>0.6</v>
-      </c>
-      <c r="E4" s="35">
-        <v>0.6</v>
-      </c>
-      <c r="F4" s="28">
-        <v>44</v>
-      </c>
-      <c r="G4" s="28">
-        <v>45</v>
-      </c>
-      <c r="H4" s="28">
-        <v>8</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="J4" s="25">
-        <v>0</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" s="35">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="35">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="28">
-        <v>42</v>
-      </c>
-      <c r="G5" s="28">
-        <v>5</v>
-      </c>
-      <c r="H5" s="28">
-        <v>3</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="J5" s="25">
-        <v>95000</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="35">
-        <v>0</v>
-      </c>
-      <c r="E6" s="35">
-        <v>0.3</v>
-      </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28">
-        <v>0</v>
-      </c>
-      <c r="H6" s="28">
-        <v>0</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="J6" s="25">
-        <v>0</v>
-      </c>
-      <c r="K6" s="30" t="s">
-        <v>344</v>
-      </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="23"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="23"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="38">
+      <c r="D11" s="37">
         <f>SUM(D4:D10)</f>
         <v>0.7</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="37">
         <f>SUM(E4:E10)</f>
         <v>1</v>
       </c>
@@ -2956,8 +3097,8 @@
         <v>1 shareholder(s) flagged for TOSI risk</v>
       </c>
       <c r="J11" s="10"/>
-      <c r="K11" s="36" t="s">
-        <v>345</v>
+      <c r="K11" s="35" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2974,32 +3115,32 @@
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="68" t="s">
-        <v>346</v>
-      </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="66"/>
+      <c r="A13" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -3008,21 +3149,21 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="A15" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="24">
         <v>25000</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>351</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>113</v>
+      <c r="C15" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -3031,34 +3172,34 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="21" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
-      <c r="K16" s="23"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
-      <c r="K17" s="23"/>
+      <c r="K17" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3129,282 +3270,282 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="24">
+        <v>120000</v>
+      </c>
+      <c r="D4" s="24">
+        <v>3867.5</v>
+      </c>
+      <c r="E4" s="24">
+        <v>396</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0</v>
+      </c>
+      <c r="G4" s="24">
+        <v>28000</v>
+      </c>
+      <c r="H4" s="24">
+        <v>6000</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="24">
+        <v>140000</v>
+      </c>
+      <c r="D5" s="24">
+        <v>3867.5</v>
+      </c>
+      <c r="E5" s="24">
+        <v>396</v>
+      </c>
+      <c r="F5" s="24">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G5" s="24">
+        <v>30000</v>
+      </c>
+      <c r="H5" s="24">
+        <v>0</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C6" s="24">
+        <v>90000</v>
+      </c>
+      <c r="D6" s="24">
+        <v>3867.5</v>
+      </c>
+      <c r="E6" s="24">
+        <v>396</v>
+      </c>
+      <c r="F6" s="24">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G6" s="24">
+        <v>17100</v>
+      </c>
+      <c r="H6" s="24">
+        <v>0</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
         <v>355</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B7" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C7" s="24">
+        <v>70000</v>
+      </c>
+      <c r="D7" s="24">
+        <v>3867.5</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0</v>
+      </c>
+      <c r="F7" s="24">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G7" s="24">
+        <v>11900</v>
+      </c>
+      <c r="H7" s="24">
+        <v>0</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
         <v>357</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B8" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="C8" s="24">
+        <v>95000</v>
+      </c>
+      <c r="D8" s="24">
+        <v>3867.5</v>
+      </c>
+      <c r="E8" s="24">
+        <v>396</v>
+      </c>
+      <c r="F8" s="24">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G8" s="24">
+        <v>18500</v>
+      </c>
+      <c r="H8" s="24">
+        <v>0</v>
+      </c>
+      <c r="I8" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="J8" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>364</v>
-      </c>
-      <c r="C4" s="25">
-        <v>120000</v>
-      </c>
-      <c r="D4" s="25">
+      <c r="B9" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="24">
+        <v>85000</v>
+      </c>
+      <c r="D9" s="24">
         <v>3867.5</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E9" s="24">
         <v>396</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F9" s="24">
+        <v>1049.1199999999999</v>
+      </c>
+      <c r="G9" s="24">
+        <v>15700</v>
+      </c>
+      <c r="H9" s="24">
         <v>0</v>
       </c>
-      <c r="G4" s="25">
-        <v>28000</v>
-      </c>
-      <c r="H4" s="25">
-        <v>6000</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="C5" s="25">
-        <v>140000</v>
-      </c>
-      <c r="D5" s="25">
-        <v>3867.5</v>
-      </c>
-      <c r="E5" s="25">
-        <v>396</v>
-      </c>
-      <c r="F5" s="25">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G5" s="25">
-        <v>30000</v>
-      </c>
-      <c r="H5" s="25">
-        <v>0</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="C6" s="25">
-        <v>90000</v>
-      </c>
-      <c r="D6" s="25">
-        <v>3867.5</v>
-      </c>
-      <c r="E6" s="25">
-        <v>396</v>
-      </c>
-      <c r="F6" s="25">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G6" s="25">
-        <v>17100</v>
-      </c>
-      <c r="H6" s="25">
-        <v>0</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="C7" s="25">
-        <v>70000</v>
-      </c>
-      <c r="D7" s="25">
-        <v>3867.5</v>
-      </c>
-      <c r="E7" s="25">
-        <v>0</v>
-      </c>
-      <c r="F7" s="25">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G7" s="25">
-        <v>11900</v>
-      </c>
-      <c r="H7" s="25">
-        <v>0</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="C8" s="25">
-        <v>95000</v>
-      </c>
-      <c r="D8" s="25">
-        <v>3867.5</v>
-      </c>
-      <c r="E8" s="25">
-        <v>396</v>
-      </c>
-      <c r="F8" s="25">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G8" s="25">
-        <v>18500</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>374</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="C9" s="25">
-        <v>85000</v>
-      </c>
-      <c r="D9" s="25">
-        <v>3867.5</v>
-      </c>
-      <c r="E9" s="25">
-        <v>396</v>
-      </c>
-      <c r="F9" s="25">
-        <v>1049.1199999999999</v>
-      </c>
-      <c r="G9" s="25">
-        <v>15700</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>374</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>365</v>
+      <c r="I9" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="15">
@@ -3435,117 +3576,117 @@
       <c r="J13" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
-        <v>376</v>
-      </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
+      <c r="A15" s="52" t="s">
+        <v>361</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
-        <v>377</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="39">
+      <c r="A16" s="54" t="s">
+        <v>362</v>
+      </c>
+      <c r="B16" s="53"/>
+      <c r="C16" s="38">
         <f>D13</f>
         <v>23205</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55" t="s">
-        <v>378</v>
-      </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="39">
+      <c r="A17" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="38">
         <f>E13</f>
         <v>1980</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
-        <v>379</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="39">
+      <c r="A18" s="54" t="s">
+        <v>364</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="38">
         <f>F13*1.4</f>
         <v>7343.8399999999983</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55" t="s">
-        <v>380</v>
-      </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="27">
+      <c r="A19" s="54" t="s">
+        <v>365</v>
+      </c>
+      <c r="B19" s="53"/>
+      <c r="C19" s="26">
         <v>600000</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55" t="s">
-        <v>381</v>
-      </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="40">
+      <c r="A20" s="54" t="s">
+        <v>366</v>
+      </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="39">
         <v>1.1499999999999999</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
-        <v>383</v>
-      </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="41">
+      <c r="A21" s="54" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" s="53"/>
+      <c r="C21" s="40">
         <f>C19/100*C20</f>
         <v>6899.9999999999991</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="64" t="s">
-        <v>384</v>
-      </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
+      <c r="A23" s="63" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3602,55 +3743,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>385</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
-        <v>386</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
+      <c r="A3" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="69" t="s">
-        <v>387</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="23" t="s">
-        <v>113</v>
+      <c r="A4" s="68" t="s">
+        <v>372</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="22" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
-        <v>388</v>
-      </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="23" t="s">
-        <v>104</v>
+      <c r="A5" s="68" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="22" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
-        <v>389</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="23" t="s">
-        <v>390</v>
+      <c r="A6" s="68" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="60"/>
+      <c r="C6" s="22" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="69" t="s">
-        <v>391</v>
-      </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="23" t="s">
-        <v>122</v>
+      <c r="A7" s="68" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="60"/>
+      <c r="C7" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3658,39 +3799,39 @@
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="63" t="s">
-        <v>392</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
+      <c r="A9" s="61" t="s">
+        <v>377</v>
+      </c>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="42">
+      <c r="A10" s="68" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="60"/>
+      <c r="C10" s="41">
         <f>'3. Income Statement'!B9</f>
         <v>1200000</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="69" t="s">
-        <v>394</v>
-      </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="23" t="s">
-        <v>395</v>
+      <c r="A11" s="68" t="s">
+        <v>379</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="22" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="69" t="s">
-        <v>396</v>
-      </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="23" t="s">
-        <v>395</v>
+      <c r="A12" s="68" t="s">
+        <v>381</v>
+      </c>
+      <c r="B12" s="60"/>
+      <c r="C12" s="22" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3698,29 +3839,29 @@
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="63" t="s">
-        <v>397</v>
-      </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
+      <c r="A14" s="61" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="69" t="s">
-        <v>398</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="43">
+      <c r="A15" s="68" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="60"/>
+      <c r="C15" s="42">
         <f>INDEX('Province Rate Reference'!$F$5:$F$17,MATCH('1. Entity Setup'!$C$12,'Province Rate Reference'!$A$5:$A$17,0))</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="69" t="s">
-        <v>399</v>
-      </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="44">
+      <c r="A16" s="68" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="43">
         <f>C10*C15</f>
         <v>60000</v>
       </c>
@@ -3730,62 +3871,62 @@
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="63" t="s">
-        <v>400</v>
-      </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
+      <c r="A18" s="61" t="s">
+        <v>385</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
     </row>
     <row r="19" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="C19" s="25">
+      <c r="A19" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="C19" s="24">
         <v>42000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="25">
+      <c r="A20" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="C20" s="24">
         <v>4000</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="C21" s="25">
+      <c r="A21" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="C21" s="24">
         <v>750</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="30" t="s">
-        <v>406</v>
-      </c>
-      <c r="C22" s="25">
+      <c r="A22" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="24">
         <v>1350</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="C23" s="27"/>
+      <c r="A23" s="28"/>
+      <c r="C23" s="26"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="29"/>
-      <c r="C24" s="27"/>
+      <c r="A24" s="28"/>
+      <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C25" s="15">
         <f>SUM(C19:C24)</f>
@@ -3797,19 +3938,19 @@
       <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="63" t="s">
-        <v>408</v>
-      </c>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
+      <c r="A27" s="61" t="s">
+        <v>393</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B28" s="19"/>
-      <c r="C28" s="45">
+      <c r="C28" s="44">
         <f>C16-C25</f>
         <v>11900</v>
       </c>
@@ -3817,7 +3958,7 @@
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C29" s="8" t="str">
         <f>IF(C28&gt;3000,"Yes - instalments likely required","No")</f>
@@ -3826,12 +3967,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:D3"/>
@@ -3841,6 +3976,12 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3885,62 +4026,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
-        <v>412</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
+      <c r="A3" s="52" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
     </row>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60" t="s">
-        <v>413</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="A4" s="62" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
-        <v>414</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="27">
+      <c r="A5" s="66" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="26">
         <v>28500</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
-        <v>415</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="27">
+      <c r="A6" s="66" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="65"/>
+      <c r="C6" s="26">
         <v>12100</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="67" t="s">
-        <v>416</v>
-      </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="27">
+      <c r="A7" s="66" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="26">
         <v>24000</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="67" t="s">
-        <v>417</v>
-      </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="27">
+      <c r="A8" s="66" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="26">
         <v>10200</v>
       </c>
     </row>
@@ -3951,7 +4092,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="8" t="str">
@@ -3965,88 +4106,88 @@
       <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63" t="s">
-        <v>419</v>
-      </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
+      <c r="A12" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="A14" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="24">
         <v>10125</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>423</v>
+      <c r="C14" s="27" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="A15" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="24">
         <v>10125</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>423</v>
+      <c r="C15" s="27" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="B16" s="27">
+      <c r="A16" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="26">
         <v>10125</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="D16" s="23"/>
+      <c r="C16" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="D16" s="22"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="27">
+      <c r="A17" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="26">
         <v>10125</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="D17" s="23"/>
+      <c r="C17" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="D17" s="22"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="B20" s="15">
         <f>SUM(B14:B19)</f>
@@ -4060,59 +4201,59 @@
       <c r="C21" s="10"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63" t="s">
-        <v>427</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
+      <c r="A22" s="61" t="s">
+        <v>412</v>
+      </c>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="67" t="s">
-        <v>428</v>
-      </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="23" t="s">
-        <v>395</v>
+      <c r="A23" s="66" t="s">
+        <v>413</v>
+      </c>
+      <c r="B23" s="65"/>
+      <c r="C23" s="22" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="67" t="s">
-        <v>429</v>
-      </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="23" t="s">
-        <v>395</v>
+      <c r="A24" s="66" t="s">
+        <v>414</v>
+      </c>
+      <c r="B24" s="65"/>
+      <c r="C24" s="22" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="67" t="s">
-        <v>430</v>
-      </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="23" t="s">
-        <v>395</v>
+      <c r="A25" s="66" t="s">
+        <v>415</v>
+      </c>
+      <c r="B25" s="65"/>
+      <c r="C25" s="22" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="67" t="s">
-        <v>431</v>
-      </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="23" t="s">
-        <v>113</v>
+      <c r="A26" s="66" t="s">
+        <v>416</v>
+      </c>
+      <c r="B26" s="65"/>
+      <c r="C26" s="22" t="s">
+        <v>98</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="67" t="s">
-        <v>433</v>
-      </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="23" t="s">
-        <v>113</v>
+      <c r="A27" s="66" t="s">
+        <v>418</v>
+      </c>
+      <c r="B27" s="65"/>
+      <c r="C27" s="22" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4167,67 +4308,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>434</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
-        <v>435</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
+      <c r="A3" s="52" t="s">
+        <v>420</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
-        <v>436</v>
-      </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="27">
+      <c r="A4" s="66" t="s">
+        <v>421</v>
+      </c>
+      <c r="B4" s="65"/>
+      <c r="C4" s="26">
         <v>65000</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
-        <v>437</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="46">
+      <c r="A5" s="66" t="s">
+        <v>422</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="45">
         <v>3000000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
-        <v>438</v>
+      <c r="A6" s="35" t="s">
+        <v>423</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="67" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="27">
+      <c r="A7" s="66" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="26">
         <v>240000</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="67" t="s">
-        <v>440</v>
-      </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="23" t="s">
-        <v>113</v>
+      <c r="A8" s="66" t="s">
+        <v>425</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="22" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="15">
@@ -4237,7 +4378,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="15">
@@ -4245,82 +4386,82 @@
         <v>22750</v>
       </c>
       <c r="D10" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="63" t="s">
-        <v>442</v>
-      </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
+      <c r="A11" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
     </row>
     <row r="12" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60" t="s">
-        <v>443</v>
-      </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
+      <c r="A12" s="62" t="s">
+        <v>428</v>
+      </c>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="67" t="s">
-        <v>444</v>
-      </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="23" t="s">
-        <v>445</v>
+      <c r="A13" s="66" t="s">
+        <v>429</v>
+      </c>
+      <c r="B13" s="65"/>
+      <c r="C13" s="22" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="67" t="s">
-        <v>446</v>
-      </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="27">
+      <c r="A14" s="66" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="65"/>
+      <c r="C14" s="26">
         <v>9750</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="67" t="s">
-        <v>542</v>
-      </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="27">
+      <c r="A15" s="66" t="s">
+        <v>527</v>
+      </c>
+      <c r="B15" s="65"/>
+      <c r="C15" s="26">
         <v>9750</v>
       </c>
       <c r="D15" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="63" t="s">
-        <v>447</v>
-      </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
+      <c r="A16" s="61" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24">
+      <c r="A18" s="23">
         <v>2025</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="24">
         <v>8000</v>
       </c>
       <c r="C18" s="8">
@@ -4328,12 +4469,12 @@
         <v>2030</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="27"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="8">
         <f>IF(A19=0,0,A19+5)</f>
         <v>0</v>
@@ -4341,18 +4482,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4390,100 +4531,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>452</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>437</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
-        <v>453</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="A5" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="24">
         <v>1000000</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <v>35000</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="24">
         <v>18000</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="24">
         <v>6200</v>
       </c>
-      <c r="G5" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>462</v>
+      <c r="G5" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
@@ -4496,66 +4637,66 @@
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="68" t="s">
-        <v>463</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="66"/>
+      <c r="A9" s="67" t="s">
+        <v>448</v>
+      </c>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
-        <v>467</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11" s="27">
+      <c r="A11" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <v>0</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="78" t="s">
-        <v>469</v>
+      <c r="H11" s="77" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="79"/>
+      <c r="H12" s="78"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
@@ -4565,63 +4706,63 @@
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="80"/>
+      <c r="H13" s="79"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="68" t="s">
-        <v>470</v>
-      </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="66"/>
+      <c r="A14" s="67" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="65"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="78" t="s">
-        <v>471</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="66"/>
+      <c r="A15" s="77" t="s">
+        <v>456</v>
+      </c>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="65"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="70" t="s">
-        <v>472</v>
-      </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="72"/>
+      <c r="A16" s="69" t="s">
+        <v>457</v>
+      </c>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="71"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="73"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="74"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="73"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="77"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4652,353 +4793,353 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>473</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>474</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="A2" s="55" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="47">
+        <v>0.23</v>
+      </c>
+      <c r="C5" s="47">
+        <v>0.11</v>
+      </c>
+      <c r="D5" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="F5" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" s="47">
+        <v>0.27</v>
+      </c>
+      <c r="C6" s="47">
+        <v>0.11</v>
+      </c>
+      <c r="D6" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="F6" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="46" t="s">
+        <v>470</v>
+      </c>
+      <c r="B7" s="47">
+        <v>0.27</v>
+      </c>
+      <c r="C7" s="47">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="F7" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="46" t="s">
+        <v>473</v>
+      </c>
+      <c r="B8" s="47">
+        <v>0.27</v>
+      </c>
+      <c r="C8" s="47">
+        <v>0.09</v>
+      </c>
+      <c r="D8" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="F8" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="47">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="C9" s="47">
+        <v>0.122</v>
+      </c>
+      <c r="D9" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E9" s="46" t="s">
         <v>476</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F9" s="49">
+        <v>0.13</v>
+      </c>
+      <c r="G9" s="35" t="s">
         <v>477</v>
       </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="46" t="s">
         <v>478</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="B10" s="47">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="C10" s="47">
+        <v>0.122</v>
+      </c>
+      <c r="D10" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E10" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="48">
-        <v>0.23</v>
-      </c>
-      <c r="C5" s="48">
+      <c r="F10" s="49">
+        <v>0.14974999999999999</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="46" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11" s="47">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C11" s="47">
+        <v>0.115</v>
+      </c>
+      <c r="D11" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="F11" s="49">
+        <v>0.15</v>
+      </c>
+      <c r="G11" s="35"/>
+    </row>
+    <row r="12" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="B12" s="47">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C12" s="47">
+        <v>0.115</v>
+      </c>
+      <c r="D12" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="F12" s="49">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46" t="s">
+        <v>484</v>
+      </c>
+      <c r="B13" s="47">
+        <v>0.31</v>
+      </c>
+      <c r="C13" s="47">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="F13" s="49">
+        <v>0.15</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="46" t="s">
+        <v>486</v>
+      </c>
+      <c r="B14" s="47">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="47">
+        <v>0.115</v>
+      </c>
+      <c r="D14" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="F14" s="49">
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="46" t="s">
+        <v>487</v>
+      </c>
+      <c r="B15" s="47">
+        <v>0.27</v>
+      </c>
+      <c r="C15" s="47">
+        <v>0.09</v>
+      </c>
+      <c r="D15" s="48">
+        <v>500000</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="F15" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="46" t="s">
+        <v>489</v>
+      </c>
+      <c r="B16" s="47">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="C16" s="47">
         <v>0.11</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D16" s="48">
         <v>500000</v>
       </c>
-      <c r="E5" s="47" t="s">
-        <v>480</v>
-      </c>
-      <c r="F5" s="50">
+      <c r="E16" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="F16" s="49">
         <v>0.05</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
-        <v>482</v>
-      </c>
-      <c r="B6" s="48">
+      <c r="G16" s="35"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="46" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="47">
         <v>0.27</v>
       </c>
-      <c r="C6" s="48">
-        <v>0.11</v>
-      </c>
-      <c r="D6" s="49">
+      <c r="C17" s="47">
+        <v>0.12</v>
+      </c>
+      <c r="D17" s="48">
         <v>500000</v>
       </c>
-      <c r="E6" s="47" t="s">
-        <v>483</v>
-      </c>
-      <c r="F6" s="50">
+      <c r="E17" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="F17" s="49">
         <v>0.05</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
-        <v>485</v>
-      </c>
-      <c r="B7" s="48">
-        <v>0.27</v>
-      </c>
-      <c r="C7" s="48">
-        <v>0.1</v>
-      </c>
-      <c r="D7" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>486</v>
-      </c>
-      <c r="F7" s="50">
-        <v>0.05</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
-        <v>488</v>
-      </c>
-      <c r="B8" s="48">
-        <v>0.27</v>
-      </c>
-      <c r="C8" s="48">
-        <v>0.09</v>
-      </c>
-      <c r="D8" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>489</v>
-      </c>
-      <c r="F8" s="50">
-        <v>0.05</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
-        <v>374</v>
-      </c>
-      <c r="B9" s="48">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="C9" s="48">
-        <v>0.122</v>
-      </c>
-      <c r="D9" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E9" s="47" t="s">
+      <c r="G17" s="35"/>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="63" t="s">
         <v>491</v>
       </c>
-      <c r="F9" s="50">
-        <v>0.13</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
-        <v>493</v>
-      </c>
-      <c r="B10" s="48">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="C10" s="48">
-        <v>0.122</v>
-      </c>
-      <c r="D10" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>494</v>
-      </c>
-      <c r="F10" s="50">
-        <v>0.14974999999999999</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
-        <v>496</v>
-      </c>
-      <c r="B11" s="48">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="C11" s="48">
-        <v>0.115</v>
-      </c>
-      <c r="D11" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>491</v>
-      </c>
-      <c r="F11" s="50">
-        <v>0.15</v>
-      </c>
-      <c r="G11" s="36"/>
-    </row>
-    <row r="12" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
-        <v>497</v>
-      </c>
-      <c r="B12" s="48">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="C12" s="48">
-        <v>0.115</v>
-      </c>
-      <c r="D12" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>491</v>
-      </c>
-      <c r="F12" s="50">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
-        <v>499</v>
-      </c>
-      <c r="B13" s="48">
-        <v>0.31</v>
-      </c>
-      <c r="C13" s="48">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E13" s="47" t="s">
-        <v>491</v>
-      </c>
-      <c r="F13" s="50">
-        <v>0.15</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
-        <v>501</v>
-      </c>
-      <c r="B14" s="48">
-        <v>0.3</v>
-      </c>
-      <c r="C14" s="48">
-        <v>0.115</v>
-      </c>
-      <c r="D14" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>491</v>
-      </c>
-      <c r="F14" s="50">
-        <v>0.15</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
-        <v>502</v>
-      </c>
-      <c r="B15" s="48">
-        <v>0.27</v>
-      </c>
-      <c r="C15" s="48">
-        <v>0.09</v>
-      </c>
-      <c r="D15" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>480</v>
-      </c>
-      <c r="F15" s="50">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47" t="s">
-        <v>504</v>
-      </c>
-      <c r="B16" s="48">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="C16" s="48">
-        <v>0.11</v>
-      </c>
-      <c r="D16" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>480</v>
-      </c>
-      <c r="F16" s="50">
-        <v>0.05</v>
-      </c>
-      <c r="G16" s="36"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="47" t="s">
-        <v>505</v>
-      </c>
-      <c r="B17" s="48">
-        <v>0.27</v>
-      </c>
-      <c r="C17" s="48">
-        <v>0.12</v>
-      </c>
-      <c r="D17" s="49">
-        <v>500000</v>
-      </c>
-      <c r="E17" s="47" t="s">
-        <v>480</v>
-      </c>
-      <c r="F17" s="50">
-        <v>0.05</v>
-      </c>
-      <c r="G17" s="36"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="s">
-        <v>506</v>
-      </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5020,253 +5161,253 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>507</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>363</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="F1" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="G1" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="H1" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>509</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>510</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>511</v>
+      <c r="A1" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>492</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>493</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>494</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>495</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -5280,7 +5421,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5290,28 +5431,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -5354,12 +5495,12 @@
       <c r="B9" s="10"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
@@ -5396,12 +5537,12 @@
       <c r="B14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
@@ -5412,75 +5553,78 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
+        <v>529</v>
+      </c>
+      <c r="B17" s="13">
+        <f>IF(SUMPRODUCT(--('3. Income Statement'!B52:B60&lt;&gt;0))&gt;0,'3. Income Statement'!B52+'3. Income Statement'!B53+'3. Income Statement'!B54+'3. Income Statement'!B55,'3. Income Statement'!B48)</f>
+        <v>55000</v>
+      </c>
+      <c r="C17" s="80" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="B18" s="15">
+        <f>MIN(500000,MAX(0,(IF('5. Prior-Year Tax Attributes'!C30="",B17,'5. Prior-Year Tax Attributes'!C30)-50000)*5))</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" s="13">
-        <f>'3. Income Statement'!B48</f>
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="15">
-        <f>MIN(500000,MAX(0,(B17-50000)*5))</f>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="B19" s="13">
         <f>'7. Associated Corporations'!E10</f>
         <v>1565000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="15">
         <f>MIN(500000,MAX(0,(B19-10000000)/40000000*500000))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>62</v>
+    <row r="21" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A21" s="81" t="s">
+        <v>60</v>
       </c>
       <c r="B21" s="15">
         <f>MAX(0,500000-MAX(B18,B20))</f>
         <v>475000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>63</v>
+    <row r="22" spans="1:4" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="81" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="15">
-        <f>MIN(B21,IF('1. Entity Setup'!$C$28="Yes",IFERROR(VLOOKUP("Northern Peak Consulting Inc. (this entity)",'7. Associated Corporations'!A5:F9,6,FALSE()),500000),500000))</f>
+        <f>MIN(B21,IF('1. Entity Setup'!$C$28="Yes",IFERROR(VLOOKUP("*"&amp;B5&amp;"*",'7. Associated Corporations'!A5:F9,6,FALSE()),500000),500000))</f>
         <v>350000</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>64</v>
+      <c r="C22" s="80" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>65</v>
+      <c r="A23" s="82" t="s">
+        <v>62</v>
       </c>
       <c r="B23" s="15">
         <f>MIN(B16,B22)</f>
         <v>190000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>66</v>
+    <row r="24" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A24" s="82" t="s">
+        <v>63</v>
       </c>
       <c r="B24" s="15">
         <f>MAX(0,B16-B22)</f>
@@ -5489,7 +5633,7 @@
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B25" s="8" t="str">
         <f>IF(B18&gt;0,"GRINDING — AAII over $50,000","OK — under $50,000 threshold")</f>
@@ -5501,299 +5645,720 @@
       <c r="B26" s="10"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="15">
+      <c r="A27" s="61" t="s">
+        <v>533</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+    </row>
+    <row r="28" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A28" s="82" t="s">
+        <v>534</v>
+      </c>
+      <c r="B28" s="8" t="str">
+        <f>IF(SUMPRODUCT(--('3. Income Statement'!B52:B60&lt;&gt;0))&gt;0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="C28" s="80" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A29" s="82" t="s">
+        <v>536</v>
+      </c>
+      <c r="B29" s="15">
+        <f>IF(B28="Yes",'3. Income Statement'!B52+'3. Income Statement'!B53,'3. Income Statement'!B48)</f>
+        <v>40000</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="82" t="s">
+        <v>538</v>
+      </c>
+      <c r="B30" s="15">
+        <f>IF(B28="Yes",'3. Income Statement'!B54+'3. Income Statement'!B55,0)</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="82" t="s">
+        <v>539</v>
+      </c>
+      <c r="B31" s="15">
+        <f>IF(B28="Yes",'3. Income Statement'!B56+'3. Income Statement'!B57,0)</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="82" t="s">
+        <v>540</v>
+      </c>
+      <c r="B32" s="15">
+        <f>B30*0.383333333333</f>
+        <v>5749.9999999950005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A33" s="82" t="s">
+        <v>541</v>
+      </c>
+      <c r="B33" s="15">
+        <f>IF(B28="Yes",'3. Income Statement'!B58+'3. Income Statement'!B59,0)</f>
+        <v>15333.33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="83" t="s">
+        <v>542</v>
+      </c>
+      <c r="B34" s="18">
+        <f>B32+B33</f>
+        <v>21083.329999995</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="82" t="s">
+        <v>543</v>
+      </c>
+      <c r="B35" s="15">
+        <f>IF(B28="Yes",'3. Income Statement'!B53,0)</f>
+        <v>20000</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="61" t="s">
+        <v>545</v>
+      </c>
+      <c r="B37" s="60"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="15">
         <f>B23*B11</f>
         <v>20900</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="15">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="15">
         <f>B24*B12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="15">
-        <f>B17*B13</f>
-        <v>25668.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="18">
-        <f>B28+B29+B30</f>
-        <v>46568.5</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="13">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="82" t="s">
+        <v>546</v>
+      </c>
+      <c r="B40" s="15">
+        <f>B29*B13</f>
+        <v>18668</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="83" t="s">
+        <v>547</v>
+      </c>
+      <c r="B41" s="18">
+        <f>B38+B39+B40</f>
+        <v>39568</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="82" t="s">
+        <v>548</v>
+      </c>
+      <c r="B42" s="15">
+        <f>B34</f>
+        <v>21083.329999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A43" s="82" t="s">
+        <v>549</v>
+      </c>
+      <c r="B43" s="15">
+        <f>0.2*B78</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="80" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A44" s="82" t="s">
+        <v>551</v>
+      </c>
+      <c r="B44" s="15">
+        <f>0.6*B80</f>
+        <v>0</v>
+      </c>
+      <c r="C44" s="80" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="B45" s="18">
+        <f>B41+B42+B43+B44</f>
+        <v>60651.329999994996</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="82" t="s">
+        <v>554</v>
+      </c>
+      <c r="B46" s="15">
+        <f>B75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A47" s="82" t="s">
+        <v>555</v>
+      </c>
+      <c r="B47" s="15">
+        <f>MIN('12. Credits &amp; Incentives'!C9+'12. Credits &amp; Incentives'!C14,MAX(0,B41))</f>
+        <v>32500</v>
+      </c>
+      <c r="C47" s="80" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="82" t="s">
+        <v>557</v>
+      </c>
+      <c r="B48" s="15">
+        <f>('12. Credits &amp; Incentives'!C10+'12. Credits &amp; Incentives'!C15)-(B47-MIN(('12. Credits &amp; Incentives'!C9-'12. Credits &amp; Incentives'!C10)+('12. Credits &amp; Incentives'!C14-'12. Credits &amp; Incentives'!C15),MAX(0,B41)))</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="80" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="83" t="s">
+        <v>559</v>
+      </c>
+      <c r="B49" s="18">
+        <f>B45-B46-B47-B48</f>
+        <v>28151.329999994996</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="15">
         <f>'11. Instalments &amp; Compliance'!B20</f>
         <v>40500</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="20">
-        <f>B31-B32</f>
-        <v>6068.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="8" t="str">
-        <f>IF(B31&gt;3000,"Yes","No")</f>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="20">
+        <f>B49-B50</f>
+        <v>-12348.670000005004</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A52" s="82" t="s">
+        <v>560</v>
+      </c>
+      <c r="B52" s="15">
+        <f>(('12. Credits &amp; Incentives'!C9-'12. Credits &amp; Incentives'!C10)+('12. Credits &amp; Incentives'!C14-'12. Credits &amp; Incentives'!C15))-MIN(('12. Credits &amp; Incentives'!C9-'12. Credits &amp; Incentives'!C10)+('12. Credits &amp; Incentives'!C14-'12. Credits &amp; Incentives'!C15),MAX(0,B41))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="8" t="str">
+        <f>IF(B41&gt;3000,"Yes","No")</f>
         <v>Yes</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-    </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-    </row>
-    <row r="37" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" s="15">
-        <f>B17*0.3067</f>
-        <v>16868.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="13">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="B55" s="60"/>
+      <c r="C55" s="60"/>
+      <c r="D55" s="60"/>
+    </row>
+    <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A56" s="82" t="s">
+        <v>562</v>
+      </c>
+      <c r="B56" s="15">
+        <f>B29*0.3067+IF(B28="Yes",'3. Income Statement'!B55*0.383333333333+'3. Income Statement'!B59,0)</f>
+        <v>27601.329999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="15">
         <f>'5. Prior-Year Tax Attributes'!C6</f>
         <v>42300</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="15">
-        <f>B38+B37</f>
-        <v>59168.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="13">
+    <row r="58" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A58" s="82" t="s">
+        <v>563</v>
+      </c>
+      <c r="B58" s="15">
+        <f>B57+B56</f>
+        <v>69901.33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A59" s="82" t="s">
+        <v>564</v>
+      </c>
+      <c r="B59" s="15">
+        <f>IF(B28="Yes",'3. Income Statement'!B54*0.383333333333+'3. Income Statement'!B58,0)</f>
+        <v>5749.9999999950005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="82" t="s">
+        <v>250</v>
+      </c>
+      <c r="B60" s="15">
         <f>'5. Prior-Year Tax Attributes'!C5</f>
         <v>18500</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="15">
-        <f>B39/0.3833</f>
-        <v>154366.0318288547</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="15">
-        <f>B40/0.3833</f>
-        <v>48265.066527524134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="13">
-        <f>'5. Prior-Year Tax Attributes'!C9</f>
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="13">
-        <f>'5. Prior-Year Tax Attributes'!C12</f>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" s="21" t="str">
-        <f>IF(B44&gt;0,"CDA balance sitting idle — consider a capital dividend election","No CDA balance available")</f>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="82" t="s">
+        <v>565</v>
+      </c>
+      <c r="B61" s="15">
+        <f>B60+B59</f>
+        <v>24249.999999995001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A62" s="82" t="s">
+        <v>566</v>
+      </c>
+      <c r="B62" s="15">
+        <f>0.72*B24+IF(B28="Yes",'3. Income Statement'!B54+'3. Income Statement'!B56,0)</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="82" t="s">
+        <v>567</v>
+      </c>
+      <c r="B63" s="15">
+        <f>'5. Prior-Year Tax Attributes'!C9+B62</f>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A64" s="82" t="s">
+        <v>568</v>
+      </c>
+      <c r="B64" s="15">
+        <f>B35+IF(B28="Yes",'3. Income Statement'!B60,0)</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="82" t="s">
+        <v>569</v>
+      </c>
+      <c r="B65" s="15">
+        <f>'5. Prior-Year Tax Attributes'!C12+B64</f>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A66" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="15">
+        <f>B58/0.383333333333</f>
+        <v>182351.29565233248</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A67" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="15">
+        <f>B61/0.383333333333</f>
+        <v>63260.86956525936</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="61" t="s">
+        <v>570</v>
+      </c>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+    </row>
+    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="82" t="s">
+        <v>202</v>
+      </c>
+      <c r="B70" s="15">
+        <f>'3. Income Statement'!B63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B71" s="15">
+        <f>'3. Income Statement'!B64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="82" t="s">
+        <v>571</v>
+      </c>
+      <c r="B72" s="15">
+        <f>'3. Income Statement'!B65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A73" s="82" t="s">
+        <v>572</v>
+      </c>
+      <c r="B73" s="15">
+        <f>MIN(B71*0.383333333333,B58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A74" s="82" t="s">
+        <v>573</v>
+      </c>
+      <c r="B74" s="15">
+        <f>MIN(B70*0.383333333333,B61)+MIN(B71*0.383333333333-B73,B61-MIN(B70*0.383333333333,B61))</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="80" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="83" t="s">
+        <v>575</v>
+      </c>
+      <c r="B75" s="18">
+        <f>B73+B74</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="82" t="s">
+        <v>576</v>
+      </c>
+      <c r="B76" s="15">
+        <f>B58-B73</f>
+        <v>69901.33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="82" t="s">
+        <v>577</v>
+      </c>
+      <c r="B77" s="15">
+        <f>B61-B74</f>
+        <v>24249.999999995001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A78" s="82" t="s">
+        <v>578</v>
+      </c>
+      <c r="B78" s="15">
+        <f>MAX(0,B70-B63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="82" t="s">
+        <v>579</v>
+      </c>
+      <c r="B79" s="15">
+        <f>MAX(0,B63-B70)</f>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A80" s="82" t="s">
+        <v>580</v>
+      </c>
+      <c r="B80" s="15">
+        <f>MAX(0,B72-B65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="82" t="s">
+        <v>581</v>
+      </c>
+      <c r="B81" s="15">
+        <f>MAX(0,B65-B72)</f>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="B82" s="21" t="str">
+        <f>IF(B81&gt;0,"CDA balance sitting idle — consider a capital dividend election","No unused CDA balance")</f>
         <v>CDA balance sitting idle — consider a capital dividend election</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-    </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="13">
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="B84" s="60"/>
+      <c r="C84" s="60"/>
+      <c r="D84" s="60"/>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" s="15">
         <f>'9. Payroll Register'!C13</f>
         <v>600000</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="13">
+    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="15">
         <f>'9. Payroll Register'!C18</f>
         <v>7343.8399999999983</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="22">
+    <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" s="20">
         <f>'10. GST-HST'!C28</f>
         <v>11900</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="13">
+    <row r="88" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A88" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="B88" s="15">
         <f>'6. CCA Continuity'!H13</f>
         <v>36900</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="13">
+    <row r="89" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A89" s="82" t="s">
+        <v>583</v>
+      </c>
+      <c r="B89" s="15">
         <f>'12. Credits &amp; Incentives'!C9</f>
         <v>22750</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" s="13">
+    <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="82" t="s">
+        <v>78</v>
+      </c>
+      <c r="B90" s="15">
         <f>'12. Credits &amp; Incentives'!C14</f>
         <v>9750</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-    </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="62" t="str">
+    <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="61" t="s">
+        <v>584</v>
+      </c>
+      <c r="B92" s="60"/>
+      <c r="C92" s="60"/>
+      <c r="D92" s="60"/>
+    </row>
+    <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="59" t="str">
         <f>IF(B18&gt;0,"• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.","")</f>
         <v>• Passive income is grinding the SBD limit — consider moving investments to a holding company or reducing corporate investment income.</v>
       </c>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-    </row>
-    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="62" t="str">
+      <c r="B93" s="60"/>
+      <c r="C93" s="60"/>
+      <c r="D93" s="60"/>
+    </row>
+    <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="59" t="str">
         <f>IF(COUNTIF('8. Shareholders &amp; TOSI'!I5:I20,"Not Excluded - TOSI Risk")&gt;0,"• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.","")</f>
         <v>• One or more shareholders flagged for TOSI risk — dividends to them may be taxed at top marginal rate.</v>
       </c>
-      <c r="B57" s="61"/>
-      <c r="C57" s="61"/>
-      <c r="D57" s="61"/>
-    </row>
-    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="62" t="str">
-        <f>IF(B44&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
+      <c r="B94" s="60"/>
+      <c r="C94" s="60"/>
+      <c r="D94" s="60"/>
+    </row>
+    <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="59" t="str">
+        <f>IF(B81&gt;0,"• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.","")</f>
         <v>• Unused Capital Dividend Account balance — a tax-free capital dividend may be available.</v>
       </c>
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-    </row>
-    <row r="59" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" s="61"/>
-      <c r="C59" s="61"/>
-      <c r="D59" s="61"/>
-    </row>
+      <c r="B95" s="60"/>
+      <c r="C95" s="60"/>
+      <c r="D95" s="60"/>
+    </row>
+    <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="59" t="str">
+        <f>IF(AND(B18&gt;0,'5. Prior-Year Tax Attributes'!C30=""),"• SBD grind uses current-year investment income as a proxy — enter the prior-year adjusted AAII on '5. Prior-Year Tax Attributes'.","")</f>
+        <v>• SBD grind uses current-year investment income as a proxy — enter the prior-year adjusted AAII on '5. Prior-Year Tax Attributes'.</v>
+      </c>
+      <c r="B96" s="60"/>
+      <c r="C96" s="60"/>
+      <c r="D96" s="60"/>
+    </row>
+    <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="59" t="str">
+        <f>IF(B34&gt;B75,"• Part IV tax exceeds this year's dividend refund — the difference sits in RDTOH until taxable dividends are paid.","")</f>
+        <v>• Part IV tax exceeds this year's dividend refund — the difference sits in RDTOH until taxable dividends are paid.</v>
+      </c>
+      <c r="B97" s="60"/>
+      <c r="C97" s="60"/>
+      <c r="D97" s="60"/>
+    </row>
+    <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="59" t="str">
+        <f>IF(B78&gt;0,"• Eligible dividends exceed GRIP — Part III.1 tax applies unless the s.185.1(2) election is filed.","")</f>
+        <v/>
+      </c>
+      <c r="B98" s="60"/>
+      <c r="C98" s="60"/>
+      <c r="D98" s="60"/>
+    </row>
+    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="59" t="str">
+        <f>IF(B80&gt;0,"• Capital dividend exceeds the CDA — 60% Part III tax unless the s.184(3) election is filed.","")</f>
+        <v/>
+      </c>
+      <c r="B99" s="60"/>
+      <c r="C99" s="60"/>
+      <c r="D99" s="60"/>
+    </row>
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="59" t="str">
+        <f>IF(B52&gt;0,"• Non-refundable credits exceed Part I tax — the excess carries forward and is NOT in the year-end balance.","")</f>
+        <v/>
+      </c>
+      <c r="B100" s="60"/>
+      <c r="C100" s="60"/>
+      <c r="D100" s="60"/>
+    </row>
+    <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="59" t="str">
+        <f>IF(B48&gt;0,"• Refundable credits exceed Part I tax — the cash refund depends on CRA / the province accepting the claim.","")</f>
+        <v/>
+      </c>
+      <c r="B101" s="60"/>
+      <c r="C101" s="60"/>
+      <c r="D101" s="60"/>
+    </row>
+    <row r="102" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" s="60"/>
+      <c r="C102" s="60"/>
+      <c r="D102" s="60"/>
+    </row>
+    <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="21">
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5815,232 +6380,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="53"/>
+      <c r="C11" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="B12" s="53"/>
+      <c r="C12" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="55" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="23" t="s">
+      <c r="B13" s="53"/>
+      <c r="C13" s="22" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="D13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="23" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="52" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="55" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="23" t="s">
+      <c r="B16" s="53"/>
+      <c r="C16" s="22" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55" t="s">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="23" t="s">
+      <c r="B17" s="53"/>
+      <c r="C17" s="22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55" t="s">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="23" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="54" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="53" t="s">
+      <c r="B19" s="53"/>
+      <c r="C19" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="23" t="s">
+      <c r="B20" s="53"/>
+      <c r="C20" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="54" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="B21" s="53"/>
+      <c r="C21" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="54" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
+      <c r="B24" s="53"/>
+      <c r="C24" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="23" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="23" t="s">
+      <c r="B28" s="53"/>
+      <c r="C28" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55" t="s">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="23">
+      <c r="B29" s="53"/>
+      <c r="C29" s="22">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A5:B5"/>
@@ -6053,18 +6630,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6112,63 +6677,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="A2" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="25">
+      <c r="A5" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="24">
         <v>850000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>420000</v>
       </c>
       <c r="D5" s="11">
@@ -6187,18 +6752,18 @@
         <f>F5*'3. Income Statement'!$B$49</f>
         <v>200687.49999999997</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>145</v>
+      <c r="H5" s="25" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="25">
+      <c r="A6" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="24">
         <v>350000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>180000</v>
       </c>
       <c r="D6" s="11">
@@ -6217,14 +6782,14 @@
         <f>F6*'3. Income Statement'!$B$49</f>
         <v>84312.5</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>147</v>
+      <c r="H6" s="25" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="11">
         <f t="shared" ref="D7:D12" si="1">IF(SUM($B$7:$B$12)=0,0,B7/SUM($B$7:$B$12))</f>
         <v>0</v>
@@ -6241,12 +6806,12 @@
         <f>F7*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H7" s="23"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6263,12 +6828,12 @@
         <f>F8*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6285,12 +6850,12 @@
         <f>F9*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6307,12 +6872,12 @@
         <f>F10*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H10" s="23"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6329,12 +6894,12 @@
         <f>F11*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H11" s="23"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6351,11 +6916,11 @@
         <f>F12*'3. Income Statement'!$B$49</f>
         <v>0</v>
       </c>
-      <c r="H12" s="23"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B14" s="15">
         <f>SUM(B5:B12)</f>
@@ -6372,8 +6937,8 @@
         <v>1</v>
       </c>
       <c r="G14" s="10"/>
-      <c r="H14" s="26" t="s">
-        <v>149</v>
+      <c r="H14" s="25" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -6416,62 +6981,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="A4" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="28">
+      <c r="A5" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="27">
         <v>850000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="28">
+      <c r="A6" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="27">
         <v>350000</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="65"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="65"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B9" s="8">
         <f>SUM(B5:B8)</f>
@@ -6483,28 +7048,28 @@
       <c r="B10" s="10"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
+      <c r="A11" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="28">
+      <c r="A12" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="27">
         <v>180000</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="23"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="22"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B14" s="8">
         <f>SUM(B12:B13)</f>
@@ -6513,7 +7078,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B15" s="8">
         <f>B9-B14</f>
@@ -6525,118 +7090,118 @@
       <c r="B16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
+      <c r="A17" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="B18" s="28">
+      <c r="A18" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="27">
         <v>600000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="A19" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="27">
         <v>60000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="28">
+      <c r="A20" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="27">
         <v>25000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="28">
+      <c r="A21" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="27">
         <v>8000</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="28">
+      <c r="A22" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="27">
         <v>15000</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" s="28">
+      <c r="A23" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="27">
         <v>10000</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" s="28">
+      <c r="A24" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="27">
         <v>45000</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="28">
+      <c r="A25" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="27">
         <v>30000</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="28">
+      <c r="A26" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="27">
         <v>20000</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" s="28">
+      <c r="A27" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="27">
         <v>12000</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="B28" s="28">
+      <c r="A28" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="27">
         <v>5000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="29"/>
-      <c r="B29" s="23"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="22"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="29"/>
-      <c r="B30" s="23"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="22"/>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B31" s="8">
         <f>SUM(B18:B30)</f>
@@ -6645,7 +7210,7 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B32" s="8">
         <f>B15-B31</f>
@@ -6657,104 +7222,104 @@
       <c r="B33" s="10"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
+      <c r="A34" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B35" s="28">
+      <c r="A35" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="27">
         <v>12000</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="B36" s="28">
+      <c r="A36" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="27">
         <v>40000</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B37" s="28">
+      <c r="A37" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="27">
         <v>15000</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="28">
+      <c r="A38" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="27">
         <v>20000</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="B39" s="28">
+      <c r="A39" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="27">
         <v>8000</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="B40" s="28">
+      <c r="A40" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="27">
         <v>0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="29"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="29"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B43" s="8">
         <f>SUM(B35:B42)</f>
@@ -6763,7 +7328,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B44" s="17">
         <f>B32+B43</f>
@@ -6777,16 +7342,16 @@
       <c r="B45" s="10"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="B46" s="61"/>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
+      <c r="A46" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="60"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="16" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B47" s="8">
         <f>B32</f>
@@ -6795,7 +7360,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B48" s="8">
         <f>SUMIF(C35:C42,"Aggregate Investment Income",B35:B42)</f>
@@ -6804,7 +7369,7 @@
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <f>B44</f>
@@ -6813,136 +7378,136 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
+        <v>182</v>
+      </c>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B52" s="28">
+        <v>183</v>
+      </c>
+      <c r="B52" s="27">
         <v>20000</v>
       </c>
       <c r="D52" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="B53" s="28">
+        <v>185</v>
+      </c>
+      <c r="B53" s="27">
         <v>20000</v>
       </c>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="B54" s="28">
+        <v>187</v>
+      </c>
+      <c r="B54" s="27">
         <v>15000</v>
       </c>
       <c r="D54" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B55" s="28"/>
+        <v>189</v>
+      </c>
+      <c r="B55" s="27"/>
       <c r="D55" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B56" s="28"/>
+        <v>191</v>
+      </c>
+      <c r="B56" s="27"/>
       <c r="D56" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="B57" s="28">
+        <v>193</v>
+      </c>
+      <c r="B57" s="27">
         <v>40000</v>
       </c>
       <c r="D57" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="B58" s="28"/>
+        <v>195</v>
+      </c>
+      <c r="B58" s="27"/>
       <c r="D58" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B59" s="28">
+        <v>197</v>
+      </c>
+      <c r="B59" s="27">
         <v>15333.33</v>
       </c>
       <c r="D59" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B60" s="28"/>
+        <v>199</v>
+      </c>
+      <c r="B60" s="27"/>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B62" s="52"/>
-      <c r="C62" s="52"/>
-      <c r="D62" s="52"/>
+        <v>201</v>
+      </c>
+      <c r="B62" s="51"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="51"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="B63" s="28"/>
+        <v>202</v>
+      </c>
+      <c r="B63" s="27"/>
       <c r="D63" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="B64" s="28"/>
+        <v>204</v>
+      </c>
+      <c r="B64" s="27"/>
       <c r="D64" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="B65" s="28"/>
+        <v>206</v>
+      </c>
+      <c r="B65" s="27"/>
       <c r="D65" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -6991,120 +7556,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="A4" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="25">
+      <c r="A5" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="24">
         <v>145000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="25">
+      <c r="A6" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="24">
         <v>210000</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="25">
+      <c r="A7" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="25">
+      <c r="A8" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="24">
         <v>15000</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="25">
+      <c r="A9" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="24">
         <v>380000</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="A10" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="24">
         <v>260000</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="A11" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="24">
         <v>100000</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="25">
+      <c r="A12" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="24">
         <v>35000</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="27"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="27"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="26"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B15" s="15">
         <f>SUM(B5:B14)</f>
@@ -7113,89 +7678,89 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="31"/>
+      <c r="B16" s="30"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="63" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
+      <c r="A17" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="A18" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="24">
         <v>95000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="25">
+      <c r="A19" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="24">
         <v>12000</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="B20" s="25">
+      <c r="A20" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="24">
         <v>40000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="B21" s="25">
+      <c r="A21" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="24">
         <v>25000</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" s="25">
+      <c r="A22" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="24">
         <v>30000</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="25">
+      <c r="A23" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="24">
         <v>150000</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="25">
+      <c r="A24" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="24">
         <v>20000</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
-      <c r="B25" s="27"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="26"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="29"/>
-      <c r="B26" s="27"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="26"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B27" s="15">
         <f>SUM(B18:B26)</f>
@@ -7204,43 +7769,43 @@
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
-      <c r="B28" s="31"/>
+      <c r="B28" s="30"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="63" t="s">
-        <v>249</v>
-      </c>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
+      <c r="A29" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="B30" s="25">
+      <c r="A30" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="24">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="B31" s="25">
+      <c r="A31" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="24">
         <v>90000</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="B32" s="25">
+      <c r="A32" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="24">
         <v>397900</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
-        <v>253</v>
+      <c r="A33" s="23" t="s">
+        <v>238</v>
       </c>
       <c r="B33" s="13">
         <f>'3. Income Statement'!B49</f>
@@ -7249,7 +7814,7 @@
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B34" s="15">
         <f>SUM(B30:B33)</f>
@@ -7258,11 +7823,11 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
-      <c r="B35" s="31"/>
+      <c r="B35" s="30"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="B36" s="15">
         <f>B27+B34</f>
@@ -7271,7 +7836,7 @@
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B37" s="15">
         <f>B15-(B27+B34)</f>
@@ -7280,35 +7845,35 @@
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
-      <c r="B38" s="31"/>
+      <c r="B38" s="30"/>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="63" t="s">
-        <v>257</v>
-      </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
+      <c r="A39" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
     </row>
     <row r="40" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B40" s="31"/>
+      <c r="A40" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="B40" s="30"/>
       <c r="D40" s="12" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B41" s="15">
         <f>B15</f>
         <v>1145000</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -7339,51 +7904,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>262</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>263</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="A2" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="A4" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="27">
+      <c r="A5" s="66" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="26">
         <v>18500</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="27">
+      <c r="A6" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="65"/>
+      <c r="C6" s="26">
         <v>42300</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7392,23 +7957,23 @@
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="63" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
+      <c r="A8" s="61" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="67" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="27">
+      <c r="A9" s="66" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="26">
         <v>65000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7417,23 +7982,23 @@
       <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="63" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
+      <c r="A11" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67" t="s">
-        <v>272</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="27">
+      <c r="A12" s="66" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="65"/>
+      <c r="C12" s="26">
         <v>22000</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7442,32 +8007,32 @@
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="63" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
+      <c r="A14" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24">
+      <c r="A16" s="23">
         <v>2022</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>15000</v>
       </c>
       <c r="C16" s="8">
@@ -7476,10 +8041,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23">
+      <c r="A17" s="22">
         <v>2023</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="22">
         <v>8000</v>
       </c>
       <c r="C17" s="8">
@@ -7488,16 +8053,16 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="8">
         <f>IF(A18=0,0,A18+20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="8">
         <f>IF(A19=0,0,A19+20)</f>
         <v>0</v>
@@ -7509,37 +8074,37 @@
       <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
+      <c r="A21" s="61" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23">
+      <c r="A23" s="22">
         <v>2021</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="22">
         <v>5000</v>
       </c>
       <c r="C23" s="10"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="10"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7548,51 +8113,45 @@
       <c r="C25" s="10"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="63" t="s">
-        <v>278</v>
-      </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
+      <c r="A26" s="61" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="67" t="s">
-        <v>279</v>
-      </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="27">
+      <c r="A27" s="66" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="65"/>
+      <c r="C27" s="26">
         <v>0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="67" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="27">
+      <c r="A28" s="66" t="s">
+        <v>266</v>
+      </c>
+      <c r="B28" s="65"/>
+      <c r="C28" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="C30" s="27"/>
+        <v>267</v>
+      </c>
+      <c r="C30" s="26"/>
       <c r="D30" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
@@ -7601,6 +8160,12 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7626,54 +8191,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>284</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
-        <v>294</v>
+      <c r="A4" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="B4" s="3">
         <v>180000</v>
@@ -7682,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -7691,7 +8256,7 @@
         <f t="shared" ref="F4:F12" si="0">B4+C4-E4-IF(D4="Yes",0,C4*0.5)</f>
         <v>180000</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="32">
         <v>0.04</v>
       </c>
       <c r="H4" s="4">
@@ -7703,12 +8268,12 @@
         <v>172800</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>296</v>
+      <c r="A5" s="31" t="s">
+        <v>281</v>
       </c>
       <c r="B5" s="3">
         <v>45000</v>
@@ -7717,7 +8282,7 @@
         <v>12000</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -7726,7 +8291,7 @@
         <f t="shared" si="0"/>
         <v>51000</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="32">
         <v>0.2</v>
       </c>
       <c r="H5" s="4">
@@ -7738,12 +8303,12 @@
         <v>46800</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
-        <v>298</v>
+      <c r="A6" s="31" t="s">
+        <v>283</v>
       </c>
       <c r="B6" s="3">
         <v>22000</v>
@@ -7752,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -7761,7 +8326,7 @@
         <f t="shared" si="0"/>
         <v>22000</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="32">
         <v>0.3</v>
       </c>
       <c r="H6" s="4">
@@ -7775,8 +8340,8 @@
       <c r="J6" s="12"/>
     </row>
     <row r="7" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
-        <v>299</v>
+      <c r="A7" s="31" t="s">
+        <v>284</v>
       </c>
       <c r="B7" s="3">
         <v>8000</v>
@@ -7785,7 +8350,7 @@
         <v>15000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -7794,7 +8359,7 @@
         <f t="shared" si="0"/>
         <v>23000</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="32">
         <v>0.55000000000000004</v>
       </c>
       <c r="H7" s="4">
@@ -7806,12 +8371,12 @@
         <v>10349.999999999998</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
-        <v>301</v>
+      <c r="A8" s="31" t="s">
+        <v>286</v>
       </c>
       <c r="B8" s="3">
         <v>5000</v>
@@ -7820,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -7829,7 +8394,7 @@
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="32">
         <v>0.05</v>
       </c>
       <c r="H8" s="4">
@@ -7841,20 +8406,20 @@
         <v>4750</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="27"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7863,19 +8428,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="23"/>
+      <c r="J9" s="22"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="27"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7884,19 +8449,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="23"/>
+      <c r="J10" s="22"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="27"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7905,19 +8470,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J11" s="23"/>
+      <c r="J11" s="22"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="27"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="26"/>
       <c r="F12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7926,11 +8491,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J12" s="23"/>
+      <c r="J12" s="22"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(B4:B12)</f>
@@ -7958,42 +8523,42 @@
       <c r="J13" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="64" t="s">
-        <v>303</v>
-      </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
+      <c r="A15" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8045,58 +8610,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>304</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>305</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="A2" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="C5" s="35">
+      <c r="A5" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" s="34">
         <v>1</v>
       </c>
       <c r="D5" s="9">
@@ -8107,66 +8672,66 @@
         <f>'4. Balance Sheet'!B41</f>
         <v>1145000</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="27">
         <v>350000</v>
       </c>
-      <c r="G5" s="26" t="s">
-        <v>314</v>
+      <c r="G5" s="25" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="35">
+      <c r="A6" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="34">
         <v>1</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="27">
         <v>60000</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <v>420000</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <v>150000</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>317</v>
+      <c r="G6" s="35" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="23"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="23"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="22"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -8185,14 +8750,14 @@
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
-        <v>318</v>
+      <c r="A11" s="25" t="s">
+        <v>303</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="37">
+      <c r="F11" s="36">
         <f>F10-500000</f>
         <v>0</v>
       </c>
@@ -8208,12 +8773,12 @@
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="67" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="23" t="s">
-        <v>113</v>
+      <c r="A13" s="66" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="65"/>
+      <c r="C13" s="22" t="s">
+        <v>98</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
